--- a/validation_1/validation/excel/validacion_o3/formulas/validacion_formula_o3_180.xlsx
+++ b/validation_1/validation/excel/validacion_o3/formulas/validacion_formula_o3_180.xlsx
@@ -233,7 +233,7 @@
     <t xml:space="preserve">Fecha de generacion</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-13 19:11:30 -0500</t>
+    <t xml:space="preserve">2026-05-13 19:21:28 -0500</t>
   </si>
   <si>
     <t xml:space="preserve">Script generador</t>
